--- a/notes/Payroll Project Test Employees - Emily Eisenhauer.xlsx
+++ b/notes/Payroll Project Test Employees - Emily Eisenhauer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2927227a20fbab87/SDEV268/Final Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2927227a20fbab87/SDEV268/Final Project/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="385" documentId="8_{6B330919-FED4-450B-ABDE-E8D36F445C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C05C871-4FF7-4F20-A293-92E713C14407}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="8_{6B330919-FED4-450B-ABDE-E8D36F445C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AE409E8-72BF-4EFD-A4C2-D38F7FFD9883}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="975" windowWidth="21600" windowHeight="11295" xr2:uid="{579332D8-70CA-4F8C-91D7-964726B243BC}"/>
+    <workbookView xWindow="-23145" yWindow="1485" windowWidth="21600" windowHeight="13470" xr2:uid="{579332D8-70CA-4F8C-91D7-964726B243BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -155,9 +155,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>alayna.ruth@businessplace.com</t>
-  </si>
-  <si>
     <t>944 Straford Park</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
     <t>Ann</t>
   </si>
   <si>
-    <t>charlotte.brooks@businessplace.com</t>
-  </si>
-  <si>
     <t>88 Lincoln Ave</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
     <t>Rae</t>
   </si>
   <si>
-    <t>olivia.bennett@businessplace.com</t>
-  </si>
-  <si>
     <t>5510 Covington Rd</t>
   </si>
   <si>
@@ -233,9 +224,6 @@
     <t>Jr.</t>
   </si>
   <si>
-    <t>ethan.foster@businessplace.com</t>
-  </si>
-  <si>
     <t>7621 Trier Rd</t>
   </si>
   <si>
@@ -248,9 +236,6 @@
     <t>Ava</t>
   </si>
   <si>
-    <t>ava.simmons@businessplace.com</t>
-  </si>
-  <si>
     <t>3108 Liberty Mills Rd</t>
   </si>
   <si>
@@ -299,18 +284,6 @@
     <t>998 Meadow Ln</t>
   </si>
   <si>
-    <t>mason.carter@businessplace.com</t>
-  </si>
-  <si>
-    <t>noah.turner@businessplace.com</t>
-  </si>
-  <si>
-    <t>morgan.harper@businessplace.com</t>
-  </si>
-  <si>
-    <t>liam.reynolds@businessplace.com</t>
-  </si>
-  <si>
     <t>Hughes</t>
   </si>
   <si>
@@ -320,9 +293,6 @@
     <t>Clare</t>
   </si>
   <si>
-    <t>emma.hughes@businessplace.com</t>
-  </si>
-  <si>
     <t>417 Birchwood Ct</t>
   </si>
   <si>
@@ -335,9 +305,6 @@
     <t>Scott</t>
   </si>
   <si>
-    <t>benjamin.price@businessplace.com</t>
-  </si>
-  <si>
     <t>250 Cherry St</t>
   </si>
   <si>
@@ -353,9 +320,6 @@
     <t>Marie</t>
   </si>
   <si>
-    <t>sophia.griffin@businessplace.com</t>
-  </si>
-  <si>
     <t>601 Westgate Blvd</t>
   </si>
   <si>
@@ -414,6 +378,42 @@
   </si>
   <si>
     <t>Base Pay</t>
+  </si>
+  <si>
+    <t>alayna.ruth1@businessplace.com</t>
+  </si>
+  <si>
+    <t>benjamin.price2@businessplace.com</t>
+  </si>
+  <si>
+    <t>liam.reynolds3@businessplace.com</t>
+  </si>
+  <si>
+    <t>noah.turner4@businessplace.com</t>
+  </si>
+  <si>
+    <t>ava.simmons5@businessplace.com</t>
+  </si>
+  <si>
+    <t>olivia.bennett6@businessplace.com</t>
+  </si>
+  <si>
+    <t>mason.carter7@businessplace.com</t>
+  </si>
+  <si>
+    <t>emma.hughes8@businessplace.com</t>
+  </si>
+  <si>
+    <t>charlotte.brooks9@businessplace.com</t>
+  </si>
+  <si>
+    <t>morgan.harper10@businessplace.com</t>
+  </si>
+  <si>
+    <t>ethan.foster11@businessplace.com</t>
+  </si>
+  <si>
+    <t>sophia.griffin12@businessplace.com</t>
   </si>
 </sst>
 </file>
@@ -455,13 +455,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -888,7 +889,7 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="U1" t="s">
         <v>19</v>
@@ -897,15 +898,15 @@
         <v>20</v>
       </c>
       <c r="W1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -931,17 +932,17 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>40</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>41</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
       </c>
       <c r="Q2">
         <v>46802</v>
@@ -964,22 +965,22 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s">
         <v>26</v>
@@ -988,22 +989,22 @@
         <v>32610</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
-        <v>99</v>
+      <c r="L3" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="M3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q3">
         <v>46750</v>
@@ -1026,25 +1027,25 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s">
         <v>26</v>
@@ -1053,25 +1054,25 @@
         <v>30684</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
         <v>22</v>
       </c>
-      <c r="L4" t="s">
-        <v>90</v>
+      <c r="L4" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="M4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q4">
         <v>46748</v>
@@ -1094,22 +1095,22 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
@@ -1118,22 +1119,22 @@
         <v>31747</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" t="s">
-        <v>88</v>
+      <c r="L5" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="M5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q5">
         <v>46748</v>
@@ -1156,19 +1157,19 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
         <v>26</v>
@@ -1182,17 +1183,17 @@
       <c r="K6" t="s">
         <v>21</v>
       </c>
-      <c r="L6" t="s">
-        <v>70</v>
+      <c r="L6" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="M6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O6" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s">
         <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
       </c>
       <c r="Q6">
         <v>46804</v>
@@ -1215,22 +1216,22 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
         <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -1244,17 +1245,17 @@
       <c r="K7" t="s">
         <v>21</v>
       </c>
-      <c r="L7" t="s">
-        <v>59</v>
+      <c r="L7" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" t="s">
         <v>41</v>
-      </c>
-      <c r="P7" t="s">
-        <v>42</v>
       </c>
       <c r="Q7">
         <v>46804</v>
@@ -1277,22 +1278,22 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
       </c>
       <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
         <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
       </c>
       <c r="H8" t="s">
         <v>26</v>
@@ -1301,22 +1302,22 @@
         <v>33311</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
       </c>
-      <c r="L8" t="s">
-        <v>87</v>
+      <c r="L8" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O8" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" t="s">
         <v>41</v>
-      </c>
-      <c r="P8" t="s">
-        <v>42</v>
       </c>
       <c r="Q8">
         <v>46802</v>
@@ -1339,22 +1340,22 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
@@ -1368,17 +1369,17 @@
       <c r="K9" t="s">
         <v>22</v>
       </c>
-      <c r="L9" t="s">
-        <v>94</v>
+      <c r="L9" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q9">
         <v>46733</v>
@@ -1401,22 +1402,22 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
       </c>
       <c r="H10" t="s">
         <v>26</v>
@@ -1430,17 +1431,17 @@
       <c r="K10" t="s">
         <v>21</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M10" t="s">
+        <v>47</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M10" t="s">
-        <v>49</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="P10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="2">
         <v>46738</v>
@@ -1463,22 +1464,22 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H11" t="s">
         <v>26</v>
@@ -1492,17 +1493,17 @@
       <c r="K11" t="s">
         <v>22</v>
       </c>
-      <c r="L11" t="s">
-        <v>89</v>
+      <c r="L11" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="M11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q11">
         <v>46773</v>
@@ -1525,25 +1526,25 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
       </c>
       <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
         <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" t="s">
-        <v>64</v>
       </c>
       <c r="H12" t="s">
         <v>26</v>
@@ -1552,25 +1553,25 @@
         <v>34883</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
       </c>
-      <c r="L12" t="s">
-        <v>65</v>
+      <c r="L12" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="M12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>46733</v>
@@ -1593,22 +1594,22 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s">
         <v>26</v>
@@ -1622,17 +1623,17 @@
       <c r="K13" t="s">
         <v>22</v>
       </c>
-      <c r="L13" t="s">
-        <v>105</v>
+      <c r="L13" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="O13" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q13">
         <v>46706</v>
